--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
+++ b/ci-build/StructureDefinition-senologie-diagnose-benigne.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3164" uniqueCount="458">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: Diagnose</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1762,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP78"/>
+  <dimension ref="A1:AR78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.25390625" customWidth="true" bestFit="true"/>
@@ -1800,12 +1806,14 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="58.4765625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="190.4140625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="29.7265625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="58.4765625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="190.4140625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1935,6 +1943,12 @@
       <c r="AP1" t="s" s="1">
         <v>78</v>
       </c>
+      <c r="AQ1" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="AR1" t="s" s="1">
+        <v>80</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1949,10 +1963,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1964,13 +1978,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -2024,22 +2038,22 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>87</v>
@@ -2048,18 +2062,24 @@
         <v>88</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="AP2" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AQ2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2067,10 +2087,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2079,19 +2099,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2141,13 +2161,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2171,15 +2191,21 @@
         <v>20</v>
       </c>
       <c r="AP3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2187,10 +2213,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2199,16 +2225,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2259,19 +2285,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2289,15 +2315,21 @@
         <v>20</v>
       </c>
       <c r="AP4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2305,31 +2337,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2379,19 +2411,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2409,15 +2441,21 @@
         <v>20</v>
       </c>
       <c r="AP5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2425,10 +2463,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2440,16 +2478,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2475,13 +2513,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2499,19 +2537,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2529,26 +2567,32 @@
         <v>20</v>
       </c>
       <c r="AP6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2560,16 +2604,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2619,19 +2663,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2643,32 +2687,38 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP7" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AQ7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2680,16 +2730,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2739,13 +2789,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2763,32 +2813,38 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP8" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2800,16 +2856,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2859,19 +2915,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2883,56 +2939,62 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -2981,19 +3043,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3005,21 +3067,27 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3027,10 +3095,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -3039,22 +3107,22 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3103,45 +3171,51 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AQ11" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AR11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3149,31 +3223,31 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3199,13 +3273,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -3223,25 +3297,25 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>167</v>
@@ -3253,15 +3327,21 @@
         <v>169</v>
       </c>
       <c r="AP12" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AQ12" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AR12" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3269,31 +3349,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3319,13 +3399,13 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>20</v>
@@ -3343,45 +3423,51 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>179</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AR13" t="s" s="2">
+        <v>182</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3389,10 +3475,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3404,16 +3490,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3439,52 +3525,52 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>189</v>
@@ -3493,15 +3579,21 @@
         <v>190</v>
       </c>
       <c r="AP14" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AQ14" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AR14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3509,10 +3601,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3524,16 +3616,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3559,52 +3651,52 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>198</v>
@@ -3614,47 +3706,53 @@
       </c>
       <c r="AP15" t="s" s="2">
         <v>200</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AR15" t="s" s="2">
+        <v>202</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3679,13 +3777,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3703,25 +3801,25 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>211</v>
@@ -3734,14 +3832,20 @@
       </c>
       <c r="AP16" t="s" s="2">
         <v>214</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AR16" t="s" s="2">
+        <v>216</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3749,10 +3853,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3764,13 +3868,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3821,13 +3925,13 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -3845,32 +3949,38 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP17" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3882,16 +3992,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3929,31 +4039,31 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3965,21 +4075,27 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3987,10 +4103,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3999,22 +4115,22 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4051,29 +4167,29 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4082,61 +4198,67 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AP19" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4146,7 +4268,7 @@
         <v>20</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>20</v>
@@ -4185,19 +4307,19 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
@@ -4206,24 +4328,30 @@
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AP20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4231,10 +4359,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4246,13 +4374,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4303,13 +4431,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4327,32 +4455,38 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4364,16 +4498,16 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4411,31 +4545,31 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4447,21 +4581,27 @@
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4469,10 +4609,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4481,22 +4621,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4545,19 +4685,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4566,24 +4706,30 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="AP23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4591,10 +4737,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4603,19 +4749,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4665,19 +4811,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4686,24 +4832,30 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="AP24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4711,10 +4863,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4723,20 +4875,20 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4785,19 +4937,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4806,24 +4958,30 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AP25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4831,10 +4989,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4843,20 +5001,20 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4905,19 +5063,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -4926,24 +5084,30 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AP26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4951,10 +5115,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4963,22 +5127,22 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5027,19 +5191,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -5048,61 +5212,67 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="AP27" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5112,7 +5282,7 @@
         <v>20</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>20</v>
@@ -5151,19 +5321,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -5172,24 +5342,30 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AP28" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5197,10 +5373,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5212,13 +5388,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5269,13 +5445,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5293,32 +5469,38 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5330,16 +5512,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5377,31 +5559,31 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5413,21 +5595,27 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP30" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5435,10 +5623,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5447,22 +5635,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5511,19 +5699,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5532,24 +5720,30 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="AP31" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5557,10 +5751,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5569,19 +5763,19 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5631,19 +5825,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5652,24 +5846,30 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="AP32" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5677,10 +5877,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5689,20 +5889,20 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5751,19 +5951,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5772,24 +5972,30 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AP33" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5797,10 +6003,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5809,20 +6015,20 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5871,19 +6077,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5892,24 +6098,30 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AP34" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5917,10 +6129,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5929,22 +6141,22 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5993,19 +6205,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -6014,61 +6226,67 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="AP35" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6078,7 +6296,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -6117,19 +6335,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6138,24 +6356,30 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AP36" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6163,10 +6387,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6178,13 +6402,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6235,13 +6459,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -6259,32 +6483,38 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6296,16 +6526,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6343,31 +6573,31 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6379,21 +6609,27 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP38" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6401,10 +6637,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6413,22 +6649,22 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6477,19 +6713,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6498,24 +6734,30 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="AP39" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR39" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6523,10 +6765,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6535,19 +6777,19 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6597,19 +6839,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6618,24 +6860,30 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="AP40" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6643,10 +6891,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6655,20 +6903,20 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6717,19 +6965,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6738,24 +6986,30 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AP41" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6763,10 +7017,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6775,20 +7029,20 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6837,19 +7091,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -6858,24 +7112,30 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AP42" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6883,10 +7143,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6895,22 +7155,22 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6959,19 +7219,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -6980,61 +7240,67 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="AP43" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7044,7 +7310,7 @@
         <v>20</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>20</v>
@@ -7083,19 +7349,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7104,24 +7370,30 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AP44" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7129,10 +7401,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7144,13 +7416,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7201,13 +7473,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -7225,32 +7497,38 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP45" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR45" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7262,16 +7540,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7309,31 +7587,31 @@
         <v>20</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7345,21 +7623,27 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP46" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7367,10 +7651,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7379,22 +7663,22 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7443,19 +7727,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7464,24 +7748,30 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="AP47" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7489,10 +7779,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7501,19 +7791,19 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7563,19 +7853,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7584,24 +7874,30 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="AP48" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7609,10 +7905,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7621,20 +7917,20 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7683,19 +7979,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7704,24 +8000,30 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AP49" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7729,10 +8031,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7741,20 +8043,20 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7803,19 +8105,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -7824,24 +8126,30 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AP50" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7849,10 +8157,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7861,22 +8169,22 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7925,19 +8233,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7946,24 +8254,30 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="AP51" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7971,10 +8285,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7983,22 +8297,22 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8047,19 +8361,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8068,24 +8382,30 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="AP52" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8093,31 +8413,31 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8143,13 +8463,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8167,45 +8487,51 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR53" t="s" s="2">
+        <v>339</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8213,10 +8539,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8228,13 +8554,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8285,13 +8611,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -8309,32 +8635,38 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP54" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR54" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8346,16 +8678,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8393,31 +8725,31 @@
         <v>20</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8429,21 +8761,27 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP55" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR55" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8451,34 +8789,34 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8527,19 +8865,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8548,24 +8886,30 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AP56" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8573,10 +8917,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8585,22 +8929,22 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8649,19 +8993,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8670,57 +9014,63 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="AP57" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR57" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8769,45 +9119,51 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>351</v>
       </c>
       <c r="AP58" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AR58" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8815,31 +9171,31 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8889,45 +9245,51 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>360</v>
       </c>
       <c r="AP59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AR59" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8935,31 +9297,31 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9009,45 +9371,51 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>369</v>
       </c>
       <c r="AP60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9055,10 +9423,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9070,16 +9438,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9129,19 +9497,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9153,21 +9521,27 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>375</v>
+        <v>20</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AR61" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9175,28 +9549,28 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9247,19 +9621,19 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
@@ -9268,24 +9642,30 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>383</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9293,10 +9673,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9305,16 +9685,16 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9365,19 +9745,19 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9389,21 +9769,27 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>388</v>
+        <v>20</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="AP63" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AR63" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9411,10 +9797,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9423,16 +9809,16 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9483,19 +9869,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9504,24 +9890,30 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>395</v>
       </c>
       <c r="AP64" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AR64" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9529,10 +9921,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9544,13 +9936,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9601,19 +9993,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -9625,21 +10017,27 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP65" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR65" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9647,10 +10045,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9662,13 +10060,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9719,13 +10117,13 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
@@ -9743,32 +10141,38 @@
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP66" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR66" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9780,16 +10184,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9839,19 +10243,19 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -9863,56 +10267,62 @@
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP67" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR67" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9961,19 +10371,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -9985,21 +10395,27 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP68" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10007,10 +10423,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -10022,13 +10438,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10055,13 +10471,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10079,45 +10495,51 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>415</v>
+        <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>212</v>
+        <v>417</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AP69" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR69" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10125,10 +10547,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10140,13 +10562,13 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10197,19 +10619,19 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AG70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -10221,21 +10643,27 @@
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP70" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10243,10 +10671,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10258,13 +10686,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10291,13 +10719,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10315,19 +10743,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10339,21 +10767,27 @@
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP71" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10361,10 +10795,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -10376,16 +10810,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10435,19 +10869,19 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -10459,21 +10893,27 @@
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP72" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR72" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10481,10 +10921,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10496,13 +10936,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10553,13 +10993,13 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
@@ -10577,32 +11017,38 @@
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP73" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR73" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -10614,16 +11060,16 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10673,19 +11119,19 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -10697,56 +11143,62 @@
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP74" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR74" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -10795,19 +11247,19 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
@@ -10819,21 +11271,27 @@
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP75" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10841,10 +11299,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -10853,16 +11311,16 @@
         <v>20</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10889,13 +11347,13 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -10913,45 +11371,51 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>20</v>
+        <v>444</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>443</v>
+        <v>189</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="AP76" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AR76" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10959,10 +11423,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -10971,16 +11435,16 @@
         <v>20</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11031,19 +11495,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -11055,21 +11519,27 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="AP77" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AR77" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11077,10 +11547,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -11092,13 +11562,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11149,41 +11619,47 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>455</v>
+        <v>20</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AP78" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP78">
+  <autoFilter ref="A1:AR78">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
